--- a/data/trans_orig/P37A$otros-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P37A$otros-Estudios-trans_orig.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8568</t>
+          <t>8184</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7921</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1306545</t>
+          <t>1306929</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2338914</t>
+          <t>2338311</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>882</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9880</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,39 +1091,39 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>0,06%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>881</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5289</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>11254</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1683533</t>
+          <t>1685208</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1692385</t>
+          <t>1692531</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,39 +1204,39 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>99,95%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1553</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1586792</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1582381</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1587673</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>99,94%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1553</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1586792</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1582384</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1587673</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>99,67%</t>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3271181</t>
+          <t>3269832</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3279342</t>
+          <t>3279348</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>471107</t>
+          <t>470466</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1021417</t>
+          <t>1021943</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>876</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10156</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>15682</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3268128</t>
+          <t>3267704</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3275663</t>
+          <t>3275667</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3369041</t>
+          <t>3368411</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3378211</t>
+          <t>3378213</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6640583</t>
+          <t>6640059</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6651935</t>
+          <t>6652016</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>6722</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1331547</t>
+          <t>1331075</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2306547</t>
+          <t>2306581</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10507</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12332</t>
+          <t>12244</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1957175</t>
+          <t>1958138</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1747296</t>
+          <t>1747089</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3709428</t>
+          <t>3709516</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3719526</t>
+          <t>3719773</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12369</t>
+          <t>12038</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14495</t>
+          <t>14358</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3413144</t>
+          <t>3413045</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3541861</t>
+          <t>3542192</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3552115</t>
+          <t>3552212</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6959517</t>
+          <t>6959654</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6970984</t>
+          <t>6970844</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>967</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8309</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>749027</t>
+          <t>748788</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>988482</t>
+          <t>987872</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1740698</t>
+          <t>1739871</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1748038</t>
+          <t>1748040</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>12939</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14575</t>
+          <t>13247</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>6346</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22577</t>
+          <t>20817</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2063077</t>
+          <t>2063446</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2074281</t>
+          <t>2074267</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1973725</t>
+          <t>1975053</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1985783</t>
+          <t>1986289</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4042108</t>
+          <t>4043868</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4057795</t>
+          <t>4058339</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12696</t>
+          <t>13290</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>880</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16912</t>
+          <t>18307</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>534190</t>
+          <t>533596</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545495</t>
+          <t>545309</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>539518</t>
+          <t>539589</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>548270</t>
+          <t>548260</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1079115</t>
+          <t>1077720</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1092621</t>
+          <t>1092101</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22326</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20045</t>
+          <t>19860</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15616</t>
+          <t>15420</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36427</t>
+          <t>37771</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3355292</t>
+          <t>3354957</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3371301</t>
+          <t>3370899</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3512055</t>
+          <t>3512240</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3526311</t>
+          <t>3526524</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6873291</t>
+          <t>6871947</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6894102</t>
+          <t>6894298</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>911</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4819</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8695</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>4208</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14753</t>
+          <t>14515</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>511812</t>
+          <t>575301</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>506182</t>
+          <t>568845</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>514063</t>
+          <t>577618</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>750689</t>
+          <t>817134</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>746813</t>
+          <t>812690</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>753726</t>
+          <t>819707</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1262501</t>
+          <t>1392435</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1255693</t>
+          <t>1386052</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1266266</t>
+          <t>1396359</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15618</t>
+          <t>16364</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9172</t>
+          <t>9061</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26636</t>
+          <t>28000</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21944</t>
+          <t>25393</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13496</t>
+          <t>16260</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35098</t>
+          <t>37570</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>37562</t>
+          <t>41757</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25116</t>
+          <t>30180</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53448</t>
+          <t>58964</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2274709</t>
+          <t>2214202</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2263691</t>
+          <t>2202566</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2281155</t>
+          <t>2221505</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2215879</t>
+          <t>2145999</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2202725</t>
+          <t>2133822</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2224327</t>
+          <t>2155132</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4490588</t>
+          <t>4360202</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4474702</t>
+          <t>4342995</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4503034</t>
+          <t>4371779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11554</t>
+          <t>13279</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>6935</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24465</t>
+          <t>25967</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14304</t>
+          <t>15988</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>22144</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12709</t>
+          <t>14194</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33972</t>
+          <t>34189</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>635069</t>
+          <t>698308</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>622158</t>
+          <t>685620</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>641248</t>
+          <t>704652</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>652397</t>
+          <t>726012</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>646159</t>
+          <t>718889</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>656008</t>
+          <t>729669</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1287465</t>
+          <t>1424320</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1273114</t>
+          <t>1412275</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1294377</t>
+          <t>1432270</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30299</t>
+          <t>32872</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19177</t>
+          <t>21831</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45696</t>
+          <t>47772</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34830</t>
+          <t>39162</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>28162</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48035</t>
+          <t>53975</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>65128</t>
+          <t>72034</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49356</t>
+          <t>55604</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84647</t>
+          <t>92587</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3421590</t>
+          <t>3487811</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3406193</t>
+          <t>3472911</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3432712</t>
+          <t>3498852</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3618964</t>
+          <t>3689145</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3605759</t>
+          <t>3674332</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3629117</t>
+          <t>3700145</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>7040555</t>
+          <t>7176956</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7021036</t>
+          <t>7156403</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7056327</t>
+          <t>7193386</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
